--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,6 +1568,130 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>109677865</v>
+      </c>
+      <c r="B9" t="n">
+        <v>96399</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222112</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Månlåsbräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Botrychium lunaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bottnane,, Dls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>339743</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6569977</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>OD-Ben-0392</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson, Anders Niklasson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Åtgärdsprogram för ärrlavar, Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,6 +1692,134 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>110868818</v>
+      </c>
+      <c r="B10" t="n">
+        <v>105852</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>245</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vårviks-Bottnane Marnäs 2, Dls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>339709</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6570012</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>OD-Ben-0407</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1820,6 +1820,390 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>110868848</v>
+      </c>
+      <c r="B11" t="n">
+        <v>105858</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>245</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>339809</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6569901</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>OD-Ben-0408</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110867122</v>
+      </c>
+      <c r="B12" t="n">
+        <v>105858</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>245</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bottnane (2), Dls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>339731</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6570050</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>OD-Ben-0406</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110867591</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105858</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Godkänd baserat på observatörens uppgifter</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>245</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bottnane (1), Dls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>339834</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6570013</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>OD-Ben-0344</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Claes Kannesten</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Roger Adolfsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1573,7 +1573,7 @@
         <v>109677865</v>
       </c>
       <c r="B9" t="n">
-        <v>96399</v>
+        <v>96406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>110868818</v>
       </c>
       <c r="B10" t="n">
-        <v>105852</v>
+        <v>105859</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110868848</v>
+        <v>110867591</v>
       </c>
       <c r="B11" t="n">
-        <v>105858</v>
+        <v>105859</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339809</v>
+        <v>339834</v>
       </c>
       <c r="R11" t="n">
-        <v>6569901</v>
+        <v>6570013</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110867122</v>
+        <v>110868848</v>
       </c>
       <c r="B12" t="n">
-        <v>105858</v>
+        <v>105859</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339731</v>
+        <v>339809</v>
       </c>
       <c r="R12" t="n">
-        <v>6570050</v>
+        <v>6569901</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867591</v>
+        <v>110867122</v>
       </c>
       <c r="B13" t="n">
-        <v>105858</v>
+        <v>105859</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339834</v>
+        <v>339731</v>
       </c>
       <c r="R13" t="n">
-        <v>6570013</v>
+        <v>6570050</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1573,7 +1573,7 @@
         <v>109677865</v>
       </c>
       <c r="B9" t="n">
-        <v>96406</v>
+        <v>96411</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>110868818</v>
       </c>
       <c r="B10" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110867591</v>
+        <v>110867122</v>
       </c>
       <c r="B11" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339834</v>
+        <v>339731</v>
       </c>
       <c r="R11" t="n">
-        <v>6570013</v>
+        <v>6570050</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1953,7 +1953,7 @@
         <v>110868848</v>
       </c>
       <c r="B12" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867122</v>
+        <v>110867591</v>
       </c>
       <c r="B13" t="n">
-        <v>105859</v>
+        <v>105864</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339731</v>
+        <v>339834</v>
       </c>
       <c r="R13" t="n">
-        <v>6570050</v>
+        <v>6570013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1573,7 +1573,7 @@
         <v>109677865</v>
       </c>
       <c r="B9" t="n">
-        <v>96411</v>
+        <v>96439</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>110868818</v>
       </c>
       <c r="B10" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110867122</v>
+        <v>110867591</v>
       </c>
       <c r="B11" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339731</v>
+        <v>339834</v>
       </c>
       <c r="R11" t="n">
-        <v>6570050</v>
+        <v>6570013</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1953,7 +1953,7 @@
         <v>110868848</v>
       </c>
       <c r="B12" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867591</v>
+        <v>110867122</v>
       </c>
       <c r="B13" t="n">
-        <v>105864</v>
+        <v>105894</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339834</v>
+        <v>339731</v>
       </c>
       <c r="R13" t="n">
-        <v>6570013</v>
+        <v>6570050</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1822,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110867591</v>
+        <v>110867122</v>
       </c>
       <c r="B11" t="n">
         <v>105894</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339834</v>
+        <v>339731</v>
       </c>
       <c r="R11" t="n">
-        <v>6570013</v>
+        <v>6570050</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110868848</v>
+        <v>110867591</v>
       </c>
       <c r="B12" t="n">
         <v>105894</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339809</v>
+        <v>339834</v>
       </c>
       <c r="R12" t="n">
-        <v>6569901</v>
+        <v>6570013</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867122</v>
+        <v>110868848</v>
       </c>
       <c r="B13" t="n">
         <v>105894</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339731</v>
+        <v>339809</v>
       </c>
       <c r="R13" t="n">
-        <v>6570050</v>
+        <v>6569901</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1573,7 +1573,7 @@
         <v>109677865</v>
       </c>
       <c r="B9" t="n">
-        <v>96439</v>
+        <v>96443</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1697,7 +1697,7 @@
         <v>110868818</v>
       </c>
       <c r="B10" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>110867122</v>
       </c>
       <c r="B11" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110867591</v>
+        <v>110868848</v>
       </c>
       <c r="B12" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339834</v>
+        <v>339809</v>
       </c>
       <c r="R12" t="n">
-        <v>6570013</v>
+        <v>6569901</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,10 +2078,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110868848</v>
+        <v>110867591</v>
       </c>
       <c r="B13" t="n">
-        <v>105894</v>
+        <v>105908</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339809</v>
+        <v>339834</v>
       </c>
       <c r="R13" t="n">
-        <v>6569901</v>
+        <v>6570013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Åtgärdsprogram för ärrlavar, Floraväkteri Sverige</t>
+          <t>Floraväkteri Sverige, Åtgärdsprogram för ärrlavar</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110867122</v>
+        <v>110867591</v>
       </c>
       <c r="B11" t="n">
         <v>105908</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339731</v>
+        <v>339834</v>
       </c>
       <c r="R11" t="n">
-        <v>6570050</v>
+        <v>6570013</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110868848</v>
+        <v>110867122</v>
       </c>
       <c r="B12" t="n">
         <v>105908</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339809</v>
+        <v>339731</v>
       </c>
       <c r="R12" t="n">
-        <v>6569901</v>
+        <v>6570050</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867591</v>
+        <v>110868848</v>
       </c>
       <c r="B13" t="n">
         <v>105908</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339834</v>
+        <v>339809</v>
       </c>
       <c r="R13" t="n">
-        <v>6570013</v>
+        <v>6569901</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige, Åtgärdsprogram för ärrlavar</t>
+          <t>Åtgärdsprogram för ärrlavar, Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110867591</v>
+        <v>110868848</v>
       </c>
       <c r="B11" t="n">
         <v>105908</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339834</v>
+        <v>339809</v>
       </c>
       <c r="R11" t="n">
-        <v>6570013</v>
+        <v>6569901</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1950,7 +1950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110867122</v>
+        <v>110867591</v>
       </c>
       <c r="B12" t="n">
         <v>105908</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339731</v>
+        <v>339834</v>
       </c>
       <c r="R12" t="n">
-        <v>6570050</v>
+        <v>6570013</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110868848</v>
+        <v>110867122</v>
       </c>
       <c r="B13" t="n">
         <v>105908</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339809</v>
+        <v>339731</v>
       </c>
       <c r="R13" t="n">
-        <v>6569901</v>
+        <v>6570050</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1950,7 +1950,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>110867591</v>
+        <v>110867122</v>
       </c>
       <c r="B12" t="n">
         <v>105908</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2002,14 +2002,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Bottnane (2), Dls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>339834</v>
+        <v>339731</v>
       </c>
       <c r="R12" t="n">
-        <v>6570013</v>
+        <v>6570050</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0406</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867122</v>
+        <v>110867591</v>
       </c>
       <c r="B13" t="n">
         <v>105908</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (2), Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339731</v>
+        <v>339834</v>
       </c>
       <c r="R13" t="n">
-        <v>6570050</v>
+        <v>6570013</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0406</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -1822,7 +1822,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>110868848</v>
+        <v>110867591</v>
       </c>
       <c r="B11" t="n">
         <v>105908</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1874,14 +1874,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
+          <t>Bottnane (1), Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>339809</v>
+        <v>339834</v>
       </c>
       <c r="R11" t="n">
-        <v>6569901</v>
+        <v>6570013</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>OD-Ben-0408</t>
+          <t>OD-Ben-0344</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -2078,7 +2078,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110867591</v>
+        <v>110868848</v>
       </c>
       <c r="B13" t="n">
         <v>105908</v>
@@ -2113,7 +2113,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2130,14 +2130,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bottnane (1), Dls</t>
+          <t>Vårviks-Bottnane Marnäs 1, Dls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>339834</v>
+        <v>339809</v>
       </c>
       <c r="R13" t="n">
-        <v>6570013</v>
+        <v>6569901</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>OD-Ben-0344</t>
+          <t>OD-Ben-0408</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">

--- a/artfynd/A 9721-2019 artfynd.xlsx
+++ b/artfynd/A 9721-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
